--- a/user/common/csv/pageindex/DigiMPGSystemGuide/DigiMPGSystemGuide.xlsx
+++ b/user/common/csv/pageindex/DigiMPGSystemGuide/DigiMPGSystemGuide.xlsx
@@ -505,7 +505,7 @@
     <t>HTTPS対応やドメイン運用を行う場合、Nginxをリバースプロキシとして配置します。以下はAzure VM + Let's Encrypt での構成例です。</t>
   </si>
   <si>
-    <t>pip / Git / apt が使えない閉域ネットワーク下の Azure 環境へ構築する場合は、ネット接続環境でビルド済みの Docker イメージを丸ごと持ち込む方式をとります。tar 化・分割転送・ロードから、Azure OpenAI への切り替え（エージェント定義の `FUNC_NAME` 変更）までの一連の手順は [SETUP_OFFLINE_DOCKER.md](SETUP_OFFLINE_DOCKER.md) を参照してください。</t>
+    <t>pip / Git / apt が使えない閉域ネットワーク下の Azure 環境へ構築する場合は、ネット接続環境でビルド済みの Docker イメージを丸ごと持ち込む方式をとります。tar 化・分割転送・ロードから、Azure OpenAI への切り替え（エージェント定義の `FUNC_NAME` 変更）までの一連の手順は [docs/SETUP_OFFLINE_DOCKER.md](docs/SETUP_OFFLINE_DOCKER.md) を参照してください。</t>
   </si>
   <si>
     <t>マスターデータは `user/common/mst/` 配下に配置します。`sample_` 付きのファイルがサンプルとして同梱されており、そのままでも動作しますが、通常は以下のようにコピーしてカスタマイズします。</t>
